--- a/data/trans_orig/P33B_R4-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R4-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>45608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67702</t>
+          <t>74831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77426</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>74008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91895</t>
+          <t>104119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>129057</t>
+          <t>146163</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112535</t>
+          <t>125769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149815</t>
+          <t>170126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>453581</t>
+          <t>492742</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437510</t>
+          <t>475787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465777</t>
+          <t>505010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>370041</t>
+          <t>400124</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355572</t>
+          <t>384292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>383188</t>
+          <t>414403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>823622</t>
+          <t>892866</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>802864</t>
+          <t>868903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>840144</t>
+          <t>913260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70372</t>
+          <t>74291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75289</t>
+          <t>84132</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62907</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90089</t>
+          <t>100119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>130373</t>
+          <t>142326</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111614</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150334</t>
+          <t>162680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396160</t>
+          <t>424030</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>380872</t>
+          <t>407933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408907</t>
+          <t>437107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>307291</t>
+          <t>339011</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292491</t>
+          <t>323024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319673</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>703451</t>
+          <t>763041</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683490</t>
+          <t>742687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722210</t>
+          <t>782947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80844</t>
+          <t>86667</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>70246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138365</t>
+          <t>106614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52569</t>
+          <t>115278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180995</t>
+          <t>154627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>586404</t>
+          <t>383966</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528883</t>
+          <t>364019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636791</t>
+          <t>400387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>140073</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115577</t>
+          <t>131050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133742</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>710924</t>
+          <t>524039</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653163</t>
+          <t>503503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>781589</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>161084</t>
+          <t>175887</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>152026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187758</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>163502</t>
+          <t>183720</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>163110</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215234</t>
+          <t>204694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>359607</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206629</t>
+          <t>327763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370880</t>
+          <t>395550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>873735</t>
+          <t>955956</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>847061</t>
+          <t>929435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893819</t>
+          <t>979817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>814185</t>
+          <t>677076</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>762453</t>
+          <t>656102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896318</t>
+          <t>697686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1687919</t>
+          <t>1633032</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1641625</t>
+          <t>1597089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1805876</t>
+          <t>1664876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>77340</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85232</t>
+          <t>96689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>208959</t>
+          <t>229293</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156049</t>
+          <t>210096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245342</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>275482</t>
+          <t>306634</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220614</t>
+          <t>281050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306109</t>
+          <t>336093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>407493</t>
+          <t>489542</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388784</t>
+          <t>470193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422698</t>
+          <t>505844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630037</t>
+          <t>600834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593654</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682947</t>
+          <t>620031</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1037530</t>
+          <t>1090375</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1006903</t>
+          <t>1060916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1092398</t>
+          <t>1115959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172817</t>
+          <t>191892</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153584</t>
+          <t>170903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191629</t>
+          <t>213941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>190890</t>
+          <t>212133</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165341</t>
+          <t>189828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>216813</t>
+          <t>239155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>222434</t>
+          <t>216987</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204260</t>
+          <t>201248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231480</t>
+          <t>226430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>587907</t>
+          <t>651648</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>569095</t>
+          <t>629599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607140</t>
+          <t>672637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>810341</t>
+          <t>868635</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>784418</t>
+          <t>841613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>835890</t>
+          <t>890940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>433239</t>
+          <t>476206</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>350904</t>
+          <t>436945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>487837</t>
+          <t>524056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>740383</t>
+          <t>824748</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>602193</t>
+          <t>784584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>813728</t>
+          <t>872582</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1173621</t>
+          <t>1300954</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1016272</t>
+          <t>1242372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1270280</t>
+          <t>1366943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2939807</t>
+          <t>2963222</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2885209</t>
+          <t>2915372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3022142</t>
+          <t>3002483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2833982</t>
+          <t>2808767</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2760637</t>
+          <t>2760933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2972172</t>
+          <t>2848931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5773789</t>
+          <t>5771989</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5677130</t>
+          <t>5706000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5931138</t>
+          <t>5830571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
